--- a/node_mapping_database.xlsx
+++ b/node_mapping_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Node Compatibility" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary &amp; Statistics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Node Compatibility" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary &amp; Statistics" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,10 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -114,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -149,6 +153,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -514,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -562,6 +567,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Custom Node File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -599,6 +609,11 @@
           <t>Map UV/Position inputs</t>
         </is>
       </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeTexCoord.json</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -636,6 +651,11 @@
           <t>Custom UV set support</t>
         </is>
       </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeUVMap.json</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -673,6 +693,11 @@
           <t>Vertex tangent space</t>
         </is>
       </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeTangent.json</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -710,6 +735,11 @@
           <t>Vertex normal vector</t>
         </is>
       </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeNormal.json</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -747,6 +777,11 @@
           <t>Simple constant</t>
         </is>
       </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeValue.json</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -784,6 +819,11 @@
           <t>Simple color constant</t>
         </is>
       </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -821,6 +861,11 @@
           <t>Custom attributes required</t>
         </is>
       </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeAttribute.json</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -858,6 +903,11 @@
           <t>Needs custom setup</t>
         </is>
       </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeLayerWeight.json</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -895,6 +945,11 @@
           <t>Direct conversion</t>
         </is>
       </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeFresnel.json</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -932,6 +987,11 @@
           <t>Hair system specific</t>
         </is>
       </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeHairInfo.json</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -969,6 +1029,11 @@
           <t>Requires C# script</t>
         </is>
       </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeObjectInfo.json</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1006,6 +1071,11 @@
           <t>Particle system dependent</t>
         </is>
       </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeParticleInfo.json</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1043,6 +1113,11 @@
           <t>Rendering-specific logic</t>
         </is>
       </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeLightPath.json</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1080,6 +1155,11 @@
           <t>Physics approximation</t>
         </is>
       </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBlackbody.json</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1117,6 +1197,11 @@
           <t>Requires texture baking</t>
         </is>
       </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeColorRamp.json</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1154,6 +1239,11 @@
           <t>Complex curves difficult</t>
         </is>
       </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeCurveRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1191,6 +1281,11 @@
           <t>Linear remapping</t>
         </is>
       </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeMapRange.json</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1228,6 +1323,11 @@
           <t>1:1 conversion</t>
         </is>
       </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeSeparateXYZ.json</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1265,6 +1365,11 @@
           <t>1:1 conversion</t>
         </is>
       </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeCombineXYZ.json</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1302,6 +1407,11 @@
           <t>Treat as XYZ</t>
         </is>
       </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeSeparateRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1339,6 +1449,11 @@
           <t>Treat as XYZ</t>
         </is>
       </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeCombineRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1450,6 +1565,11 @@
           <t>Full parity with Unity</t>
         </is>
       </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeVectorMath.json</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1524,6 +1644,11 @@
           <t>May need custom shader</t>
         </is>
       </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeVectorRotate.json</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1561,6 +1686,11 @@
           <t>Custom implementation</t>
         </is>
       </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeVectorTransform.json</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1598,6 +1728,11 @@
           <t>3D texture support</t>
         </is>
       </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeMapping.json</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1635,6 +1770,11 @@
           <t>Color space aware</t>
         </is>
       </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeNormalMap.json</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1672,6 +1812,11 @@
           <t>Approximation needed</t>
         </is>
       </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBump.json</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1709,6 +1854,11 @@
           <t>Quality depends on mesh</t>
         </is>
       </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeDisplacement.json</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1746,6 +1896,11 @@
           <t>Complete parity</t>
         </is>
       </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeMath.json</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1783,6 +1938,11 @@
           <t>Shader composition</t>
         </is>
       </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeAddShader.json</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1820,6 +1980,11 @@
           <t>Linear blend</t>
         </is>
       </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeMixShader.json</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1857,6 +2022,11 @@
           <t>Blend modes differ</t>
         </is>
       </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeMixRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1894,6 +2064,11 @@
           <t>Min/Max limiting</t>
         </is>
       </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeClamp.json</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1931,6 +2106,11 @@
           <t>Physics-based color</t>
         </is>
       </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBlackbody.json</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2005,6 +2185,11 @@
           <t>Difficult to replicate</t>
         </is>
       </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeCurveRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2042,6 +2227,11 @@
           <t>Requires approximation</t>
         </is>
       </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeShaderToRGB.json</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2079,6 +2269,11 @@
           <t>Most complex conversion</t>
         </is>
       </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfPrincipled.json</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2116,6 +2311,11 @@
           <t>Basic PBR</t>
         </is>
       </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfDiffuse.json</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2153,6 +2353,11 @@
           <t>Approximate</t>
         </is>
       </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfGlossy.json</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2190,6 +2395,11 @@
           <t>Requires composition</t>
         </is>
       </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfGlass.json</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2227,6 +2437,11 @@
           <t>Simple transparency</t>
         </is>
       </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfTransparent.json</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2264,6 +2479,11 @@
           <t>Approximation</t>
         </is>
       </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfRefraction.json</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2301,6 +2521,11 @@
           <t>Difficult without SSS</t>
         </is>
       </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfTranslucent.json</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2338,6 +2563,11 @@
           <t>Works but no bloom auto</t>
         </is>
       </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeEmission.json</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2375,6 +2605,11 @@
           <t>Requires custom code</t>
         </is>
       </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfAnisotropic.json</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2412,6 +2647,11 @@
           <t>Complex to approximate</t>
         </is>
       </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfSheen.json</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2449,6 +2689,11 @@
           <t>Requires gradient ramp</t>
         </is>
       </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBsdfToon.json</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -2486,6 +2731,11 @@
           <t>Complex custom shader</t>
         </is>
       </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeSubsurfaceScattering.json</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2560,6 +2810,11 @@
           <t>Compositor only</t>
         </is>
       </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeHoldout.json</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2597,6 +2852,11 @@
           <t>Cycles volumetric only</t>
         </is>
       </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeVolumeAbsorption.json</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -2634,6 +2894,11 @@
           <t>Cycles volumetric only</t>
         </is>
       </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeVolumeScatter.json</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2671,6 +2936,11 @@
           <t>Cannot replicate in RT</t>
         </is>
       </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeLightFalloff.json</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -2708,6 +2978,11 @@
           <t>Must pre-bake in Blender</t>
         </is>
       </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeAmbientOcclusion.json</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2745,6 +3020,11 @@
           <t>Core texture sampling</t>
         </is>
       </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeTexImage.json</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2782,6 +3062,11 @@
           <t>Similar workflow</t>
         </is>
       </c>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeTexEnvironment.json</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -3189,6 +3474,11 @@
           <t>Bake-only feature</t>
         </is>
       </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeTexPointDensity.json</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -3263,6 +3553,11 @@
           <t>Painted vertex colors</t>
         </is>
       </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeVertexColor.json</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3300,6 +3595,11 @@
           <t>Fresnel + Facing approximation</t>
         </is>
       </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeLayerWeight.json</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3337,6 +3637,11 @@
           <t>Simple inversion</t>
         </is>
       </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeInvert.json</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3374,6 +3679,11 @@
           <t>Helper node</t>
         </is>
       </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeReroute.json</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -3411,6 +3721,11 @@
           <t>Instancing metadata</t>
         </is>
       </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeArrayInfo.json</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3448,8 +3763,77 @@
           <t>Physics-based</t>
         </is>
       </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>data/custom_nodes/ShaderNodeBlackbody.json</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
